--- a/AuctionDraft/draft_data.xlsx
+++ b/AuctionDraft/draft_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69d4d5ddfe981a73/Documents/GitHub/GTS/AuctionDraft/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{5F2CF8A8-11E3-4F31-B4C4-B3F1E97719A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79019A79-63E3-40B5-B901-733DC2C4496D}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{5F2CF8A8-11E3-4F31-B4C4-B3F1E97719A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26E5ED0A-84C8-4008-9808-F0A1261EE7CE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8DA97CE2-F849-4CEE-A062-B329036B66E3}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Players" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Players!$A$1:$B$314</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Players!$A$1:$B$436</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="457">
   <si>
     <t>Team</t>
   </si>
@@ -66,18 +66,12 @@
     <t>Snooze</t>
   </si>
   <si>
-    <t>KingZ</t>
-  </si>
-  <si>
     <t>Cole</t>
   </si>
   <si>
     <t>Bagge</t>
   </si>
   <si>
-    <t>Labelle</t>
-  </si>
-  <si>
     <t>Mo</t>
   </si>
   <si>
@@ -108,943 +102,1315 @@
     <t>TE</t>
   </si>
   <si>
-    <t>Barkley, Saquon PHI</t>
-  </si>
-  <si>
-    <t>Nacua, Puka LAR</t>
-  </si>
-  <si>
-    <t>St. Brown, Amon-Ra DET</t>
-  </si>
-  <si>
-    <t>Higgins, Tee CIN</t>
-  </si>
-  <si>
-    <t>Jacobs, Josh GBP</t>
-  </si>
-  <si>
-    <t>Brown, A.J. PHI</t>
-  </si>
-  <si>
-    <t>Evans, Mike TBB</t>
-  </si>
-  <si>
-    <t>Hill, Tyreek MIA</t>
-  </si>
-  <si>
-    <t>McLaurin, Terry WAS</t>
-  </si>
-  <si>
-    <t>Metcalf, DK PIT</t>
-  </si>
-  <si>
-    <t>Sutton, Courtland DEN</t>
-  </si>
-  <si>
-    <t>McCaffrey, Christian SFO</t>
-  </si>
-  <si>
-    <t>Montgomery, David DET</t>
-  </si>
-  <si>
-    <t>Smith, DeVonta PHI</t>
-  </si>
-  <si>
-    <t>Swift, D'Andre CHI</t>
-  </si>
-  <si>
-    <t>Jeudy, Jerry CLE</t>
-  </si>
-  <si>
-    <t>Mahomes, Patrick KCC</t>
-  </si>
-  <si>
-    <t>Andrews, Mark BAL</t>
-  </si>
-  <si>
-    <t>Murray, Kyler ARI</t>
-  </si>
-  <si>
-    <t>Waddle, Jaylen MIA</t>
-  </si>
-  <si>
-    <t>Samuel, Deebo WAS</t>
-  </si>
-  <si>
-    <t>Jeanty, Ashton LVR</t>
-  </si>
-  <si>
-    <t>Hampton, Omarion LAC</t>
-  </si>
-  <si>
-    <t>Mason, Jordan MIN</t>
-  </si>
-  <si>
-    <t>Ekeler, Austin WAS</t>
-  </si>
-  <si>
-    <t>Henderson, TreVeyon NEP</t>
-  </si>
-  <si>
-    <t>Jennings, Jauan SFO</t>
-  </si>
-  <si>
-    <t>Kraft, Tucker GBP</t>
-  </si>
-  <si>
-    <t>Harvey, RJ DEN</t>
-  </si>
-  <si>
-    <t>Hunter, Travis JAC</t>
-  </si>
-  <si>
-    <t>McMillan, Tetairoa CAR</t>
-  </si>
-  <si>
-    <t>Pitts, Kyle ATL</t>
-  </si>
-  <si>
-    <t>Fields, Justin NYJ</t>
-  </si>
-  <si>
-    <t>Egbuka, Emeka TBB</t>
-  </si>
-  <si>
-    <t>Johnson, Kaleb PIT</t>
-  </si>
-  <si>
-    <t>Golden, Matthew GBP</t>
-  </si>
-  <si>
-    <t>Warren, Tyler IND</t>
-  </si>
-  <si>
-    <t>Harris, Najee LAC</t>
-  </si>
-  <si>
-    <t>Lawrence, Trevor JAC</t>
-  </si>
-  <si>
-    <t>McCarthy, J.J. MIN</t>
-  </si>
-  <si>
-    <t>Loveland, Colston CHI</t>
-  </si>
-  <si>
-    <t>Allen, Keenan LAC</t>
-  </si>
-  <si>
-    <t>Croskey-Merritt, Jacory WAS</t>
-  </si>
-  <si>
-    <t>Skattebo, Cam NYG</t>
-  </si>
-  <si>
-    <t>Tagovailoa, Tua MIA</t>
-  </si>
-  <si>
-    <t>Ertz, Zach WAS</t>
-  </si>
-  <si>
-    <t>Penix Jr., Michael ATL</t>
-  </si>
-  <si>
-    <t>Judkins, Quinshon CLE</t>
-  </si>
-  <si>
-    <t>Stafford, Matthew LAR</t>
-  </si>
-  <si>
-    <t>Dowdle, Rico CAR</t>
-  </si>
-  <si>
-    <t>Hunt, Kareem KCC</t>
-  </si>
-  <si>
-    <t>Likely, Isaiah BAL</t>
-  </si>
-  <si>
-    <t>Rodgers, Aaron PIT</t>
-  </si>
-  <si>
-    <t>Blue, Jaydon DAL</t>
-  </si>
-  <si>
-    <t>Ward, Cam TEN</t>
-  </si>
-  <si>
-    <t>Higgins, Jayden HOU</t>
-  </si>
-  <si>
-    <t>Johnston, Quentin LAC</t>
-  </si>
-  <si>
-    <t>Tillman, Cedric CLE</t>
-  </si>
-  <si>
-    <t>Strange, Brenton JAC</t>
-  </si>
-  <si>
-    <t>Tuten, Bhayshul JAC</t>
-  </si>
-  <si>
-    <t>Brown, Marquise KCC</t>
-  </si>
-  <si>
-    <t>Burden, Luther CHI</t>
-  </si>
-  <si>
-    <t>Otton, Cade TBB</t>
-  </si>
-  <si>
-    <t>Gordon, Ollie MIA</t>
-  </si>
-  <si>
-    <t>Mixon, Joe HOU</t>
-  </si>
-  <si>
-    <t>Palmer, Joshua BUF</t>
-  </si>
-  <si>
-    <t>Sampson, Dylan CLE</t>
-  </si>
-  <si>
-    <t>Guerendo, Isaac SFO</t>
-  </si>
-  <si>
-    <t>Cooper, Amari LVR</t>
-  </si>
-  <si>
-    <t>Johnson, Roschon CHI</t>
-  </si>
-  <si>
-    <t>Wilson, Russell NYG</t>
-  </si>
-  <si>
-    <t>Taylor, Mason NYJ</t>
-  </si>
-  <si>
-    <t>Gesicki, Mike CIN</t>
-  </si>
-  <si>
-    <t>Hopkins, DeAndre BAL</t>
-  </si>
-  <si>
-    <t>Lockett, Tyler TEN</t>
-  </si>
-  <si>
-    <t>Shipley, Will PHI</t>
-  </si>
-  <si>
-    <t>Jones, Daniel IND</t>
-  </si>
-  <si>
-    <t>Miller, Kendre NOS</t>
-  </si>
-  <si>
-    <t>Harris, Tre LAC</t>
-  </si>
-  <si>
-    <t>Mitchell, Keaton BAL</t>
-  </si>
-  <si>
-    <t>Williams, Kyle NEP</t>
-  </si>
-  <si>
-    <t>Mostert, Raheem LVR</t>
-  </si>
-  <si>
-    <t>Dart, Jaxson NYG</t>
-  </si>
-  <si>
-    <t>Marks, Woody HOU</t>
-  </si>
-  <si>
-    <t>Thornton, Dont'e LVR</t>
-  </si>
-  <si>
-    <t>Tucker, Tre LVR</t>
-  </si>
-  <si>
-    <t>Pierce, Dameon HOU</t>
-  </si>
-  <si>
-    <t>Singletary, Devin NYG</t>
-  </si>
-  <si>
-    <t>TeSlaa, Isaac DET</t>
-  </si>
-  <si>
-    <t>Franklin, Troy DEN</t>
-  </si>
-  <si>
-    <t>Johnson, Juwan NOS</t>
-  </si>
-  <si>
-    <t>Rodriguez, Chris WAS</t>
-  </si>
-  <si>
-    <t>Waller, Darren MIA</t>
-  </si>
-  <si>
-    <t>Arroyo, Elijah SEA</t>
-  </si>
-  <si>
-    <t>Austin III, Calvin PIT</t>
-  </si>
-  <si>
-    <t>Bech, Jack LVR</t>
-  </si>
-  <si>
-    <t>Flacco, Joe CLE</t>
-  </si>
-  <si>
-    <t>Johnson, Theo NYG</t>
-  </si>
-  <si>
-    <t>Sanders, Ja'Tavion CAR</t>
-  </si>
-  <si>
-    <t>Tucker, Sean TBB</t>
-  </si>
-  <si>
-    <t>Cousins, Kirk ATL</t>
-  </si>
-  <si>
-    <t>Gray, Noah KCC</t>
-  </si>
-  <si>
-    <t>Horton, Tory SEA</t>
-  </si>
-  <si>
-    <t>Tolbert, Jalen DAL</t>
-  </si>
-  <si>
-    <t>Bryant, Pat DEN</t>
-  </si>
-  <si>
-    <t>Giddens, DJ IND</t>
-  </si>
-  <si>
-    <t>Sanders, Miles DAL</t>
-  </si>
-  <si>
-    <t>Slayton, Darius NYG</t>
-  </si>
-  <si>
-    <t>Wilson, Emanuel GBP</t>
-  </si>
-  <si>
-    <t>Ayomanor, Elic TEN</t>
-  </si>
-  <si>
-    <t>Higbee, Tyler LAR</t>
-  </si>
-  <si>
-    <t>McCloud, Ray-Ray ATL</t>
-  </si>
-  <si>
-    <t>Monangai, Kyle CHI</t>
-  </si>
-  <si>
-    <t>Rattler, Spencer NOS</t>
-  </si>
-  <si>
-    <t>Wilson, Roman PIT</t>
-  </si>
-  <si>
-    <t>Brooks, Tahj CIN</t>
-  </si>
-  <si>
-    <t>Ferguson, Terrance LAR</t>
-  </si>
-  <si>
-    <t>Noel, Jaylin HOU</t>
-  </si>
-  <si>
-    <t>Fannin, Harold CLE</t>
-  </si>
-  <si>
-    <t>Boutte, Kayshon NEP</t>
-  </si>
-  <si>
-    <t>Gibson, Antonio NEP</t>
-  </si>
-  <si>
-    <t>Hunter, Jarquez LAR</t>
-  </si>
-  <si>
-    <t>Smith, Brashard KCC</t>
-  </si>
-  <si>
-    <t>Etienne, Trevor CAR</t>
-  </si>
-  <si>
-    <t>Fant, Noah CIN</t>
-  </si>
-  <si>
-    <t>Nailor, Jalen MIN</t>
-  </si>
-  <si>
-    <t>Royals, Jalen KCC</t>
-  </si>
-  <si>
-    <t>Shough, Tyler NOS</t>
-  </si>
-  <si>
-    <t>Sinnott, Ben WAS</t>
-  </si>
-  <si>
-    <t>Sanders, Shedeur CLE</t>
-  </si>
-  <si>
-    <t>Washington, Malik MIA</t>
-  </si>
-  <si>
-    <t>Atwell, Tutu LAR</t>
-  </si>
-  <si>
-    <t>Coker, Jalen CAR</t>
-  </si>
-  <si>
-    <t>Conklin, Tyler LAC</t>
-  </si>
-  <si>
-    <t>Dissly, Will LAC</t>
-  </si>
-  <si>
-    <t>Milroe, Jalen SEA</t>
-  </si>
-  <si>
-    <t>Neal, Devin NOS</t>
-  </si>
-  <si>
-    <t>Vele, Devaughn NOS</t>
-  </si>
-  <si>
-    <t>Barner, AJ SEA</t>
-  </si>
-  <si>
-    <t>Bond, Isaiah CLE</t>
-  </si>
-  <si>
-    <t>Musgrave, Luke GBP</t>
-  </si>
-  <si>
-    <t>White, Zamir LVR</t>
-  </si>
-  <si>
-    <t>Brown, Dyami JAC</t>
-  </si>
-  <si>
-    <t>Johnson, Ty BUF</t>
-  </si>
-  <si>
-    <t>Westbrook-Ikhine, Nick MIA</t>
-  </si>
-  <si>
-    <t>James, Jordan SFO</t>
-  </si>
-  <si>
-    <t>Lazard, Allen NYJ</t>
-  </si>
-  <si>
-    <t>Mitchell, Elijah KCC</t>
-  </si>
-  <si>
-    <t>Perine, Samaje CIN</t>
-  </si>
-  <si>
-    <t>Watson, Christian GBP</t>
-  </si>
-  <si>
-    <t>Whittington, Jordan LAR</t>
-  </si>
-  <si>
-    <t>Davis, Isaiah NYJ</t>
-  </si>
-  <si>
-    <t>Gadsden, Oronde LAC</t>
-  </si>
-  <si>
-    <t>Knox, Dawson BUF</t>
-  </si>
-  <si>
-    <t>Lambert-Smith, KeAndre LAC</t>
-  </si>
-  <si>
-    <t>Winston, Jameis NYG</t>
-  </si>
-  <si>
-    <t>Dillon, AJ PHI</t>
-  </si>
-  <si>
-    <t>Estime, Audric PHI</t>
-  </si>
-  <si>
-    <t>Lane, Jaylin WAS</t>
-  </si>
-  <si>
-    <t>Pickett, Kenny LVR</t>
-  </si>
-  <si>
-    <t>Turpin, KaVontae DAL</t>
-  </si>
-  <si>
-    <t>Brown, Noah WAS</t>
-  </si>
-  <si>
-    <t>Metchie, John PHI</t>
-  </si>
-  <si>
-    <t>Washington, Parker JAC</t>
-  </si>
-  <si>
-    <t>Williams, Savion GBP</t>
-  </si>
-  <si>
-    <t>Willis, Malik GBP</t>
-  </si>
-  <si>
-    <t>Chism, Efton NEP</t>
-  </si>
-  <si>
-    <t>Samuel, Curtis BUF</t>
-  </si>
-  <si>
-    <t>Schoonmaker, Luke DAL</t>
-  </si>
-  <si>
-    <t>Gabriel, Dillon CLE</t>
-  </si>
-  <si>
-    <t>Garoppolo, Jimmy LAR</t>
-  </si>
-  <si>
-    <t>Helm, Gunnar TEN</t>
-  </si>
-  <si>
-    <t>Jones, Mac SFO</t>
-  </si>
-  <si>
-    <t>Milton, Joe DAL</t>
-  </si>
-  <si>
-    <t>Felton, Tai MIN</t>
-  </si>
-  <si>
-    <t>Hooper, Austin NEP</t>
-  </si>
-  <si>
-    <t>Hyatt, Jalin NYG</t>
-  </si>
-  <si>
-    <t>Smith-Schuster, JuJu KCC</t>
-  </si>
-  <si>
-    <t>Howell, Sam PHI</t>
-  </si>
-  <si>
-    <t>Minshew, Gardner KCC</t>
-  </si>
-  <si>
-    <t>Rudolph, Mason PIT</t>
-  </si>
-  <si>
-    <t>Stover, Cade HOU</t>
-  </si>
-  <si>
-    <t>Dortch, Greg ARI</t>
-  </si>
-  <si>
-    <t>Hill, Taysom NOS</t>
-  </si>
-  <si>
-    <t>Lance, Trey LAC</t>
-  </si>
-  <si>
-    <t>Zaccheaus, Olamide CHI</t>
-  </si>
-  <si>
-    <t>Browning, Jake CIN</t>
-  </si>
-  <si>
-    <t>Valdes-Scantling, Marquez SFO</t>
-  </si>
-  <si>
-    <t>Demercado, Emari ARI</t>
-  </si>
-  <si>
-    <t>Moore, Skyy SFO</t>
-  </si>
-  <si>
-    <t>Washington, Darnell PIT</t>
-  </si>
-  <si>
-    <t>Wilson, Zach MIA</t>
-  </si>
-  <si>
-    <t>Dike, Chimere TEN</t>
-  </si>
-  <si>
-    <t>Ewers, Quinn MIA</t>
-  </si>
-  <si>
-    <t>Hollins, Mack NEP</t>
-  </si>
-  <si>
-    <t>Mariota, Marcus WAS</t>
-  </si>
-  <si>
-    <t>Mullings, Kalel TEN</t>
-  </si>
-  <si>
-    <t>Patrick, Tim JAC</t>
-  </si>
-  <si>
-    <t>Rush, Cooper BAL</t>
-  </si>
-  <si>
-    <t>Taylor, Tyrod NYJ</t>
-  </si>
-  <si>
-    <t>Tremble, Tommy CAR</t>
-  </si>
-  <si>
-    <t>Allen, LeQuint JAC</t>
-  </si>
-  <si>
-    <t>Bellinger, Daniel NYG</t>
-  </si>
-  <si>
-    <t>Brissett, Jacoby ARI</t>
-  </si>
-  <si>
-    <t>Brooks, Jonathon CAR</t>
-  </si>
-  <si>
-    <t>Corley, Malachi CLE</t>
-  </si>
-  <si>
-    <t>Dalton, Andy CAR</t>
-  </si>
-  <si>
-    <t>Howard, Will PIT</t>
-  </si>
-  <si>
-    <t>Jefferson, Van TEN</t>
-  </si>
-  <si>
-    <t>Johnson, Tez TBB</t>
-  </si>
-  <si>
-    <t>Mattison, Alexander MIA</t>
-  </si>
-  <si>
-    <t>McNichols, Jeremy WAS</t>
-  </si>
-  <si>
-    <t>Parkinson, Colby LAR</t>
-  </si>
-  <si>
-    <t>Polk, Ja'Lynn NEP</t>
-  </si>
-  <si>
-    <t>Raymond, Kalif DET</t>
-  </si>
-  <si>
-    <t>Walker, Devontez BAL</t>
-  </si>
-  <si>
-    <t>Bagent, Tyson CHI</t>
-  </si>
-  <si>
-    <t>Calcaterra, Grant PHI</t>
-  </si>
-  <si>
-    <t>Horn, Jimmy CAR</t>
-  </si>
-  <si>
-    <t>Lock, Drew SEA</t>
-  </si>
-  <si>
-    <t>Watkins, Jordan SFO</t>
-  </si>
-  <si>
-    <t>Watson, Deshaun CLE</t>
-  </si>
-  <si>
-    <t>Ali, Rasheen BAL</t>
-  </si>
-  <si>
-    <t>Brooks, Chris GBP</t>
-  </si>
-  <si>
-    <t>Goodson, Tyler IND</t>
-  </si>
-  <si>
-    <t>Jones, Zay ARI</t>
-  </si>
-  <si>
-    <t>Levis, Will TEN</t>
-  </si>
-  <si>
-    <t>McKee, Tanner PHI</t>
-  </si>
-  <si>
-    <t>Mingo, Jonathan DAL</t>
-  </si>
-  <si>
-    <t>Palmer, Trey NOS</t>
-  </si>
-  <si>
-    <t>Restrepo, Xavier TEN</t>
-  </si>
-  <si>
-    <t>Smith, Arian NYJ</t>
-  </si>
-  <si>
-    <t>Thornton, Tyquan KCC</t>
-  </si>
-  <si>
-    <t>Wiley, Jared KCC</t>
-  </si>
-  <si>
-    <t>Bennett, Stetson LAR</t>
-  </si>
-  <si>
-    <t>Higgins, Elijah ARI</t>
-  </si>
-  <si>
-    <t>Moreau, Foster NOS</t>
-  </si>
-  <si>
-    <t>O'Connell, Aidan LVR</t>
-  </si>
-  <si>
-    <t>Oliver, Josh MIN</t>
-  </si>
-  <si>
-    <t>Sanders, Raheim CLE</t>
-  </si>
-  <si>
-    <t>Shepard, Sterling TBB</t>
-  </si>
-  <si>
-    <t>Thrash, Jamari CLE</t>
-  </si>
-  <si>
-    <t>Trubisky, Mitchell BUF</t>
-  </si>
-  <si>
-    <t>Chestnut, Julius TEN</t>
-  </si>
-  <si>
-    <t>Cowing, Jacob SFO</t>
-  </si>
-  <si>
-    <t>Hutchinson, Xavier HOU</t>
-  </si>
-  <si>
-    <t>Mafah, Phil DAL</t>
-  </si>
-  <si>
-    <t>Mills, Davis HOU</t>
-  </si>
-  <si>
-    <t>Sermon, Trey PIT</t>
-  </si>
-  <si>
-    <t>Trautman, Adam DEN</t>
-  </si>
-  <si>
-    <t>Wentz, Carson MIN</t>
-  </si>
-  <si>
-    <t>Woods, Jelani NYJ</t>
-  </si>
-  <si>
-    <t>Woods, Robert PIT</t>
-  </si>
-  <si>
-    <t>Abanikanda, Israel GBP</t>
-  </si>
-  <si>
-    <t>All, Erick CIN</t>
-  </si>
-  <si>
-    <t>Davis, Derius LAC</t>
-  </si>
-  <si>
-    <t>Dobbs, Joshua NEP</t>
-  </si>
-  <si>
-    <t>Evans, Mitchell CAR</t>
-  </si>
-  <si>
-    <t>Granson, Kylen PHI</t>
-  </si>
-  <si>
-    <t>Leonard, Riley IND</t>
-  </si>
-  <si>
-    <t>Renfrow, Hunter CAR</t>
-  </si>
-  <si>
-    <t>Ruckert, Jeremy NYJ</t>
-  </si>
-  <si>
-    <t>Stidham, Jarrett DEN</t>
-  </si>
-  <si>
-    <t>Vaki, Sione DET</t>
-  </si>
-  <si>
-    <t>Alie-Cox, Mo IND</t>
-  </si>
-  <si>
-    <t>Bobo, Jake SEA</t>
-  </si>
-  <si>
-    <t>Edwards, Donovan WAS</t>
-  </si>
-  <si>
-    <t>Fidone, Thomas NYG</t>
-  </si>
-  <si>
-    <t>Gipson, Xavier NYJ</t>
-  </si>
-  <si>
-    <t>Hardman, Mecole GBP</t>
-  </si>
-  <si>
-    <t>Haskins, Hassan LAC</t>
-  </si>
-  <si>
-    <t>Holani, George SEA</t>
-  </si>
-  <si>
-    <t>Hudson, Tanner CIN</t>
-  </si>
-  <si>
-    <t>Kolar, Charlie BAL</t>
-  </si>
-  <si>
-    <t>Moore, David CAR</t>
-  </si>
-  <si>
-    <t>Moore, Rondale MIN</t>
-  </si>
-  <si>
-    <t>Mumpfield, Konata LAR</t>
-  </si>
-  <si>
-    <t>Ogunbowale, Dare HOU</t>
-  </si>
-  <si>
-    <t>Reiman, Tip ARI</t>
-  </si>
-  <si>
-    <t>Smartt, Stone NYJ</t>
-  </si>
-  <si>
-    <t>Strong Jr., Pierre CLE</t>
-  </si>
-  <si>
-    <t>Tinsley, Mitchell CIN</t>
-  </si>
-  <si>
-    <t>Watson, Justin HOU</t>
-  </si>
-  <si>
-    <t>Badie, Tyler DEN</t>
-  </si>
-  <si>
-    <t>Durham, Payne TBB</t>
-  </si>
-  <si>
-    <t>Gore Jr., Frank BUF</t>
-  </si>
-  <si>
-    <t>Gray, Eric NYG</t>
-  </si>
-  <si>
-    <t>Juszczyk, Kyle SFO</t>
-  </si>
-  <si>
-    <t>Mullens, Nick JAC</t>
-  </si>
-  <si>
-    <t>Mundt, Johnny JAC</t>
-  </si>
-  <si>
-    <t>Reynolds, Craig DET</t>
-  </si>
-  <si>
-    <t>Tipton, Mason NOS</t>
-  </si>
-  <si>
-    <t>Wilson, Jeffery MIA</t>
-  </si>
-  <si>
-    <t>Wright, Brock DET</t>
-  </si>
-  <si>
-    <t>Allen, Davis LAR</t>
-  </si>
-  <si>
-    <t>Bryant, Harrison HOU</t>
-  </si>
-  <si>
-    <t>DeVito, Tommy NEP</t>
-  </si>
-  <si>
-    <t>Duvernay, Devin CHI</t>
-  </si>
-  <si>
-    <t>Haener, Jake NOS</t>
-  </si>
-  <si>
-    <t>Hill, Julian MIA</t>
-  </si>
-  <si>
-    <t>Humphrey, Lil'Jordan NYG</t>
-  </si>
-  <si>
-    <t>Huntley, Tyler BAL</t>
-  </si>
-  <si>
-    <t>Jordan, Brevin HOU</t>
-  </si>
-  <si>
-    <t>Krull, Lucas DEN</t>
-  </si>
-  <si>
-    <t>Means, Bub NOS</t>
-  </si>
-  <si>
-    <t>Sample, Drew CIN</t>
-  </si>
-  <si>
-    <t>Spann-Ford, Brevyn DAL</t>
-  </si>
-  <si>
-    <t>Taylor, Patrick SFO</t>
-  </si>
-  <si>
-    <t>Wilson, Johnny PHI</t>
-  </si>
-  <si>
-    <t>Chandler, Ty MIN</t>
-  </si>
-  <si>
-    <t>Cooks, Brandin NOS</t>
-  </si>
-  <si>
-    <t>Kupp, Cooper SEA</t>
-  </si>
-  <si>
-    <t>Etienne, Travis JAC</t>
+    <t>Dom</t>
+  </si>
+  <si>
+    <t>Brian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown, Chase CIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pickens, George DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, Drake ATL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collins, Nico HOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hall, Breece NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamb, CeeDee DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olave, Chris NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Jr., Marvin ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Williams, Jameson DET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurts, Jalen PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jefferson, Justin MIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, Jordan GBP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charbonnet, Zach SEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worthy, Xavier KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stafford, Matthew LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moore, D.J. BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracy, Tyrone NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robinson, Wan'Dale TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meyers, Jakobi JAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierce, Alec IND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goedert, Dallas PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilson, Michael ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darnold, Sam SEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelce, Travis KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doubs, Romeo NEP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young, Bryce CAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">White, Rachaad WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuel, Deebo FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henry, Hunter NEP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacheco, Isiah DET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reed, Jayden GBP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaheed, Rashid SEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilson, Garrett NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jones, Aaron MIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnson, Juwan NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kamara, Alvin NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gadsden, Oronde LAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likely, Isaiah NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coleman, Keon BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boutte, Kayshon NEP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Washington, Parker JAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucker, Tre LVR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schultz, Dalton HOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barner, AJ SEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brissett, Jacoby ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vidal, Kimani LAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">McCarthy, J.J. MIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Njoku, David LAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodriguez, Chris JAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodgers, Aaron PIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupp, Cooper SEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shough, Tyler NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilson, Emanuel SEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otton, Cade TBB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell, Adonai NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freiermuth, Pat PIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benson, Trey ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engram, Evan DEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown, Marquise PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Washington, Malik MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dike, Chimere TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legette, Xavier CAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mims, Marvin DEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mooney, Darnell NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith, Geno NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnson, Kaleb PIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conner, James ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brooks, Jonathon CAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hill, Tyreek FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ridley, Calvin TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanders, Shedeur CLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gordon, Ollie MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunt, Kareem FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cousins, Kirk LVR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dell, Tank HOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willis, Malik MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singletary, Devin NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fields, Justin KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parkinson, Colby LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neal, Devin NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kmet, Cole CHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirk, Christian SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noel, Jaylin HOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonges, Jake SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slayton, Darius NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mayer, Michael LVR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ferguson, Terrance LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jones, Mac SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm, Gunnar TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chubb, Nick FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richardson, Anthony IND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nailor, Jalen LVR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harris, Najee FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tillman, Cedric CLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixon, Joe FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flournoy, Ryan DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnson, Tez TBB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesicki, Mike CIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davis, Isaiah NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ertz, Zach FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hill, Justice BAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miller, Kendre NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">McCaffrey, Luke WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austin III, Calvin NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iosivas, Andrei CIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watson, Deshaun CLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bond, Isaiah CLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fant, Noah NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariota, Marcus WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Musgrave, Luke GBP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith, Jonnu FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thornton, Tyquan KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knox, Dawson BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thornton, Dont'e LVR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Love, Jeremiyah ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vele, Devaughn NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gray, Noah KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etienne, Trevor CAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tate, Carnell TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rattler, Spencer NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">James, Jordan SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flacco, Joe CIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milroe, Jalen SEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemon, Makai PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyson, Jordyn NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmer, Joshua BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinnott, Ben WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hollins, Mack NEP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price, Jadarian SEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turpin, KaVontae DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demercado, Emari KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guerendo, Isaac SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brooks, Tahj CIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royals, Jalen KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sadiq, Kenyon NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnson, Ty BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concepcion, KC CLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carter, Michael TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipley, Will PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tolbert, Jalen MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Washington, Darnell PIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bourne, Kendrick ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perine, Samaje CIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metchie, John CAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mendoza, Fernando LVR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Williams, Antonio WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coleman, Jonah DEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Jr., Omar NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boston, Denzel CLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hopkins, DeAndre FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter, Jarquez LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dulcich, Greg MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hutchinson, Xavier HOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dotson, Jahan ATL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilson, Roman PIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ewers, Quinn MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allen, LeQuint JAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stowers, Eli PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singleton, Nicholas TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higbee, Tyler LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bernard, Germie PIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Williams, Savion GBP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ekeler, Austin FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winston, Jameis NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lane, Jaylin WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriel, Dillon CLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Washington Jr., Mike LVR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davis, Malik DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnson, Emmett KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch, Zachariah ATL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allen, Kaytron WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stribling, De'Zhaun SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bell, Chris MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fields, Malachi NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knight, Bam ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hill, Taysom NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurst, Ted TBB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazzell II, Chris CAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Howard, Will PIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnson, Roschon CHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zaccheaus, Olamide ATL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brooks, Chris GBP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black, Kaelon SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milton, Joe DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lane, Ja'Kobi BAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bell, Skyler BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claiborne, Demond MIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sarratt, Elijah BAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estime, Audric NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">McNichols, Jeremy WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mills, Davis HOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taylor, Tyrod GBP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burks, Treylon WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simpson, Ty LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klare, Max LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atwell, Tutu MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith-Schuster, JuJu NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">McLaughlin, Jaleel DEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beck, Carson ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delp, Oscar NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Randall, Adam BAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dortch, Greg DET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whittington, Jordan LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Douglas, Caleb MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown, Dyami WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lance, Trey LAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levis, Will TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lockett, Tyler FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas, Zavion CHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raridon, Eli NEP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pickett, Kenny CAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joly, Justin DEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minshew, Gardner ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tremble, Tommy CAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hooper, Austin ATL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thompson, Brenen LAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostert, Raheem LVR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allar, Drew PIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lance, Bryce NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shepard, Sterling TBB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilson, Russell FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bellinger, Daniel TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stover, Cade HOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schoonmaker, Luke DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonard, Riley IND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierce, Dameon PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooks, Brandin BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polk, Ja'Lynn NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moore, Elijah PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lambert-Smith, KeAndre LAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagent, Tyson CHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">McKee, Tanner PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanders, Miles FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">All, Erick CIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanders, Raheim CLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rudolph, Mason PIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">McGowan, Seth IND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heidenreich, Eli PIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klubnik, Cade NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felton, Tai MIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mafah, Phil DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evans, Mitchell CAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walker, Devontez BAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan, Jawhar HOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conklin, Tyler DET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Westbrook-Ikhine, Nick IND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robinson, Demarcus SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higgins, Elijah ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horn, Jimmy CAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klein, Marlin HOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mumpfield, Konata LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Browning, Jake TBB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali, Rasheen BAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huntley, Tyler BAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mattison, Alexander MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garoppolo, Jimmy LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyatt, Jalin NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dillon, AJ CAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilson, Zach NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allen, Cyrus KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chism, Efton NEP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coleman, Kevin MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wentz, Carson MIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raymond, Kalif CHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalton, Andy PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holani, George SEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allen, Davis LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burks, Deion IND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Howell, Sam DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thielen, Adam FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">White, Zamir FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hawes, Jackson BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jefferson, Van WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boerkircher, Nate JAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davis, Gabriel BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trubisky, Mitchell TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dissly, Will FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green, Taylen CLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown, Noah WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hibner, Matthew BAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mingo, Jonathan DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock, Drew SEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cowing, Jacob SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martinez, Damien GBP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigg, Michael DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver, Josh MIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trautman, Adam DEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wright, Brock DET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corley, Malachi CLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'Connell, Aidan LVR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moore, Skyy GBP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roush, Sam CHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniels, CJ LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watkins, Jordan SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">McCloud, Ray-Ray NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nussmeier, Garrett KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott, Zavier MIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reynolds, Josh NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiley, Jared KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burton, Jermaine FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haskins, Hassan LAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koziol, Tanner JAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lazard, Allen FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell, Elijah PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moreau, Foster HOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mullings, Kalel TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuel, Curtis FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavers, Tyrell BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Williams, Isaiah NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jones, Zay ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kolar, Charlie LAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick, Tim NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chandler, Ty NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miller, Jam NEP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badie, Tyler DEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payton, Cole PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stidham, Jarrett DEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juszczyk, Kyle SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruckert, Jeremy NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaterra, Grant PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kacmarek, Will MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bates, John WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith, Arian NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young, Colbie CIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akers, Cam FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cook, Brady NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endries, Jack CIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnson, Kameron TBB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restrepo, Xavier TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rivers, Philip IND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long, Hunter JAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laube, Dylan LVR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Means, Bub NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goodson, Tyler ATL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abdullah, Ameer JAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benson, Malik LVR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caldwell, Jeff KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renfrow, Hunter FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valdes-Scantling, Marquez DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tinsley, Mitchell CIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bennett, Stetson LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan, Brevin HOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ott, Jaydn KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmer, Trey NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price, Myles MIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taylor, J'Mari JAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hudson, Tanner CIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reiman, Tip ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">McIntosh, Kenny SEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granson, Kylen TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jennings, Terrell NEP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mullens, Nick JAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaki, Sione DET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridgewater, Teddy DET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beckham, Odell NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brosmer, Max MIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown, Barion NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carr, Derek FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duvernay, Devin ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edwards, Donovan MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbert, Khalil NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jones, Charlie CIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rush, Cooper FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thrash, Jamari CLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample, Drew CIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walker, Jahdae CHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alie-Cox, Mo IND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davis, Derius LAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traore, Seydou MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gray, Eric NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abanikanda, Israel DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baker, Javon SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chestnut, Julius TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edwards-Helaire, Clyde KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gore Jr., Frank BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gyllenborg, John Michael KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henry, Robert WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hill, Julian NEP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hooker, Hendon TEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnson, Tyler DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ogunbowale, Dare HOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilson, Johnny PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Woods, Jelani NYJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farrell, Luke SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durham, Payne TBB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith, Xavier LAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dulin, Ashton IND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humphrey, Lil'Jordan DEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bobo, Jake SEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipton, Mason NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hodgins, Isaiah NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watson, Justin HOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mundt, Johnny PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royer, Joe CLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong Jr., Pierre GBP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carter, Nathan ATL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allen, Kyle BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper, Amari FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dobbs, Joshua FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidone, Thomas NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardman, Mecole BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnson, Diontae FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moss, Le'Veon MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moss, Zack FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sermon, Trey PIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virgil, Reggie ARI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wetjen, Kaden PIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moore, David CAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spann-Ford, Brevyn DAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remigio, Nikko KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper, Darius PHI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sills, David TBB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skowronek, Ben PIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eskridge, Dee MIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gould, Anthony IND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bryant, Harrison SEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collins, Beaux NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallace, Tylan CLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briningstool, Jake KCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron, Josh JAC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gipson, Xavier NYG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hemby, Roman LVR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hines, Nyheim NOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larison, Lan NEP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Law, Kendrick DET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moore, Chris WAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavia, Diego BAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reid, Desmond BUF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reynolds, Craig NEP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rice, Brenden GBP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruggs, Henry FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taylor, Patrick SFO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaughn, Deuce FA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Washington, Casey ATL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilson, Jeffery MIA </t>
   </si>
 </sst>
 </file>
@@ -1080,9 +1446,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1098,6 +1463,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1439,44 +1808,44 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1484,125 +1853,125 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="D6">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1">
-        <v>203</v>
-      </c>
-      <c r="D7" s="1">
-        <v>36</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>109</v>
+      </c>
+      <c r="D7">
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C8">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="D10">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>11</v>
       </c>
       <c r="C11">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="D11">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C12">
-        <v>259</v>
+        <v>99</v>
       </c>
       <c r="D12">
-        <v>70</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
         <v>15</v>
       </c>
-      <c r="B13">
-        <v>25</v>
-      </c>
       <c r="C13">
-        <v>259</v>
+        <v>75</v>
       </c>
       <c r="D13">
-        <v>70</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1612,19 +1981,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C3FECB-4F86-4C70-ACEE-A6019369A1F8}">
-  <dimension ref="A1:B314"/>
+  <dimension ref="A1:B436"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1632,7 +2001,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1640,7 +2009,7 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1648,7 +2017,7 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1656,7 +2025,7 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1664,7 +2033,7 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1672,7 +2041,7 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1680,7 +2049,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1688,7 +2057,7 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1696,7 +2065,7 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1704,7 +2073,7 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1712,7 +2081,7 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1728,7 +2097,7 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1736,7 +2105,7 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1752,7 +2121,7 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1760,7 +2129,7 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1768,7 +2137,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1776,7 +2145,7 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -1784,7 +2153,7 @@
         <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1800,7 +2169,7 @@
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1816,7 +2185,7 @@
         <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1824,7 +2193,7 @@
         <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1840,7 +2209,7 @@
         <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1848,7 +2217,7 @@
         <v>49</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1856,7 +2225,7 @@
         <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1864,7 +2233,7 @@
         <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1872,7 +2241,7 @@
         <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1880,7 +2249,7 @@
         <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1888,7 +2257,7 @@
         <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1896,7 +2265,7 @@
         <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1904,7 +2273,7 @@
         <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1912,7 +2281,7 @@
         <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1920,7 +2289,7 @@
         <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1928,7 +2297,7 @@
         <v>59</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1936,7 +2305,7 @@
         <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -1944,7 +2313,7 @@
         <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1952,7 +2321,7 @@
         <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -1960,7 +2329,7 @@
         <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1968,7 +2337,7 @@
         <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -1976,12 +2345,12 @@
         <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>334</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
         <v>18</v>
@@ -1989,55 +2358,55 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B53" t="s">
         <v>18</v>
@@ -2045,47 +2414,47 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B54" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B56" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B59" t="s">
         <v>19</v>
@@ -2093,55 +2462,55 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B60" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B61" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B63" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B65" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B66" t="s">
         <v>18</v>
@@ -2149,47 +2518,47 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B68" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B71" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B72" t="s">
         <v>18</v>
@@ -2197,119 +2566,119 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B74" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B75" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B76" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B77" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B80" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B81" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B82" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B83" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B84" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B85" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B86" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B87" t="s">
         <v>19</v>
@@ -2317,7 +2686,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B88" t="s">
         <v>19</v>
@@ -2325,7 +2694,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B89" t="s">
         <v>18</v>
@@ -2333,175 +2702,175 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B90" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B91" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B93" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B94" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B95" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B96" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B97" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B98" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B99" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B100" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B101" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B102" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B103" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B104" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B105" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B106" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B107" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B108" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B109" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B110" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>332</v>
+        <v>131</v>
       </c>
       <c r="B111" t="s">
         <v>19</v>
@@ -2509,7 +2878,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>333</v>
+        <v>132</v>
       </c>
       <c r="B112" t="s">
         <v>19</v>
@@ -2517,15 +2886,15 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B113" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B114" t="s">
         <v>19</v>
@@ -2533,175 +2902,175 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B115" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B116" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B117" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B118" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B119" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B120" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B121" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B122" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B123" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B124" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B125" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B126" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B127" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B128" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B129" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B130" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B131" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B132" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B133" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B134" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B135" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B136" t="s">
         <v>19</v>
@@ -2709,47 +3078,47 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B137" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B138" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B139" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B140" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B141" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B142" t="s">
         <v>19</v>
@@ -2757,31 +3126,31 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B143" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B144" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B145" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B146" t="s">
         <v>18</v>
@@ -2789,87 +3158,87 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B147" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B148" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B149" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B150" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B151" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B152" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B153" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B154" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B155" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B156" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>331</v>
+        <v>177</v>
       </c>
       <c r="B157" t="s">
         <v>18</v>
@@ -2877,399 +3246,399 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B158" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B159" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B160" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B161" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B162" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B163" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B164" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B165" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B166" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B167" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B168" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B169" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B170" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B171" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B172" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B173" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B174" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B175" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B176" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B177" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B178" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B179" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B180" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B181" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B182" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B183" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B184" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B185" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B186" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B187" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B188" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B189" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B190" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B191" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B192" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B193" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B194" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B195" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B196" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B197" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B198" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B199" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B200" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B201" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B202" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B203" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B204" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B205" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B206" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B207" t="s">
         <v>18</v>
@@ -3277,31 +3646,31 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B208" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B209" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B210" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B211" t="s">
         <v>19</v>
@@ -3309,31 +3678,31 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B212" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B213" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B214" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B215" t="s">
         <v>19</v>
@@ -3341,71 +3710,71 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B216" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B217" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B218" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B219" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B220" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B221" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B222" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B223" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B224" t="s">
         <v>19</v>
@@ -3413,87 +3782,87 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B225" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B226" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B227" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B228" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B229" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B230" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B231" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B232" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B233" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B234" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B235" t="s">
         <v>19</v>
@@ -3501,87 +3870,87 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B236" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B237" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B238" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B239" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B240" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B241" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B242" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B243" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B244" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B245" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B246" t="s">
         <v>19</v>
@@ -3589,39 +3958,39 @@
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B247" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B248" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B249" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B250" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B251" t="s">
         <v>19</v>
@@ -3629,191 +3998,191 @@
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B252" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B253" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B254" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B255" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B256" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B257" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B258" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B259" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B260" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B261" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B262" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B263" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B264" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B265" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B266" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B267" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B268" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B269" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B270" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B271" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B272" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B273" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B274" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B275" t="s">
         <v>19</v>
@@ -3821,15 +4190,15 @@
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B276" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B277" t="s">
         <v>18</v>
@@ -3837,31 +4206,31 @@
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B278" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B279" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B280" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B281" t="s">
         <v>19</v>
@@ -3869,15 +4238,15 @@
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B282" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B283" t="s">
         <v>18</v>
@@ -3885,31 +4254,31 @@
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B284" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B285" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B286" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B287" t="s">
         <v>19</v>
@@ -3917,7 +4286,7 @@
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B288" t="s">
         <v>19</v>
@@ -3925,23 +4294,23 @@
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B289" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B290" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B291" t="s">
         <v>18</v>
@@ -3949,95 +4318,95 @@
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B292" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B293" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B294" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B295" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B296" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B297" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B298" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B299" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B300" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B301" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B302" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B303" t="s">
         <v>19</v>
@@ -4045,23 +4414,23 @@
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B304" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B305" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B306" t="s">
         <v>19</v>
@@ -4069,70 +4438,1045 @@
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B307" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B308" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B309" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B310" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B311" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B312" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B313" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B314" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>335</v>
+      </c>
+      <c r="B315" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>336</v>
+      </c>
+      <c r="B316" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>337</v>
+      </c>
+      <c r="B317" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>338</v>
+      </c>
+      <c r="B318" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>339</v>
+      </c>
+      <c r="B319" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>340</v>
+      </c>
+      <c r="B320" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>341</v>
+      </c>
+      <c r="B321" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>342</v>
+      </c>
+      <c r="B322" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>343</v>
+      </c>
+      <c r="B323" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>344</v>
+      </c>
+      <c r="B324" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>345</v>
+      </c>
+      <c r="B325" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>346</v>
+      </c>
+      <c r="B326" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>347</v>
+      </c>
+      <c r="B327" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>348</v>
+      </c>
+      <c r="B328" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>349</v>
+      </c>
+      <c r="B329" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>350</v>
+      </c>
+      <c r="B330" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>351</v>
+      </c>
+      <c r="B331" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>352</v>
+      </c>
+      <c r="B332" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>353</v>
+      </c>
+      <c r="B333" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>354</v>
+      </c>
+      <c r="B334" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>355</v>
+      </c>
+      <c r="B335" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>356</v>
+      </c>
+      <c r="B336" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>357</v>
+      </c>
+      <c r="B337" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>358</v>
+      </c>
+      <c r="B338" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>359</v>
+      </c>
+      <c r="B339" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>360</v>
+      </c>
+      <c r="B340" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>361</v>
+      </c>
+      <c r="B341" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>362</v>
+      </c>
+      <c r="B342" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>363</v>
+      </c>
+      <c r="B343" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>364</v>
+      </c>
+      <c r="B344" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>365</v>
+      </c>
+      <c r="B345" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>366</v>
+      </c>
+      <c r="B346" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>367</v>
+      </c>
+      <c r="B347" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>368</v>
+      </c>
+      <c r="B348" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>369</v>
+      </c>
+      <c r="B349" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>370</v>
+      </c>
+      <c r="B350" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>371</v>
+      </c>
+      <c r="B351" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>372</v>
+      </c>
+      <c r="B352" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>373</v>
+      </c>
+      <c r="B353" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>374</v>
+      </c>
+      <c r="B354" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>375</v>
+      </c>
+      <c r="B355" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>376</v>
+      </c>
+      <c r="B356" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>377</v>
+      </c>
+      <c r="B357" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>378</v>
+      </c>
+      <c r="B358" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>379</v>
+      </c>
+      <c r="B359" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>380</v>
+      </c>
+      <c r="B360" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>381</v>
+      </c>
+      <c r="B361" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>382</v>
+      </c>
+      <c r="B362" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>383</v>
+      </c>
+      <c r="B363" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>384</v>
+      </c>
+      <c r="B364" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>385</v>
+      </c>
+      <c r="B365" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>386</v>
+      </c>
+      <c r="B366" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>387</v>
+      </c>
+      <c r="B367" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>388</v>
+      </c>
+      <c r="B368" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>389</v>
+      </c>
+      <c r="B369" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>390</v>
+      </c>
+      <c r="B370" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>391</v>
+      </c>
+      <c r="B371" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>392</v>
+      </c>
+      <c r="B372" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>393</v>
+      </c>
+      <c r="B373" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>394</v>
+      </c>
+      <c r="B374" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>395</v>
+      </c>
+      <c r="B375" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>396</v>
+      </c>
+      <c r="B376" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>397</v>
+      </c>
+      <c r="B377" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>398</v>
+      </c>
+      <c r="B378" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>399</v>
+      </c>
+      <c r="B379" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>400</v>
+      </c>
+      <c r="B380" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>401</v>
+      </c>
+      <c r="B381" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>402</v>
+      </c>
+      <c r="B382" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>403</v>
+      </c>
+      <c r="B383" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>404</v>
+      </c>
+      <c r="B384" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>405</v>
+      </c>
+      <c r="B385" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>406</v>
+      </c>
+      <c r="B386" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>407</v>
+      </c>
+      <c r="B387" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>408</v>
+      </c>
+      <c r="B388" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>409</v>
+      </c>
+      <c r="B389" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>410</v>
+      </c>
+      <c r="B390" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>411</v>
+      </c>
+      <c r="B391" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>412</v>
+      </c>
+      <c r="B392" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>413</v>
+      </c>
+      <c r="B393" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>414</v>
+      </c>
+      <c r="B394" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>415</v>
+      </c>
+      <c r="B395" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>416</v>
+      </c>
+      <c r="B396" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>417</v>
+      </c>
+      <c r="B397" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>418</v>
+      </c>
+      <c r="B398" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>419</v>
+      </c>
+      <c r="B399" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>420</v>
+      </c>
+      <c r="B400" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>421</v>
+      </c>
+      <c r="B401" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>422</v>
+      </c>
+      <c r="B402" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>423</v>
+      </c>
+      <c r="B403" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>424</v>
+      </c>
+      <c r="B404" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>425</v>
+      </c>
+      <c r="B405" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>426</v>
+      </c>
+      <c r="B406" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>427</v>
+      </c>
+      <c r="B407" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>428</v>
+      </c>
+      <c r="B408" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>429</v>
+      </c>
+      <c r="B409" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>430</v>
+      </c>
+      <c r="B410" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>431</v>
+      </c>
+      <c r="B411" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>432</v>
+      </c>
+      <c r="B412" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>433</v>
+      </c>
+      <c r="B413" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>434</v>
+      </c>
+      <c r="B414" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>435</v>
+      </c>
+      <c r="B415" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>436</v>
+      </c>
+      <c r="B416" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>437</v>
+      </c>
+      <c r="B417" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>438</v>
+      </c>
+      <c r="B418" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>439</v>
+      </c>
+      <c r="B419" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>440</v>
+      </c>
+      <c r="B420" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>441</v>
+      </c>
+      <c r="B421" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>442</v>
+      </c>
+      <c r="B422" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>443</v>
+      </c>
+      <c r="B423" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>444</v>
+      </c>
+      <c r="B424" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>445</v>
+      </c>
+      <c r="B425" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>446</v>
+      </c>
+      <c r="B426" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>447</v>
+      </c>
+      <c r="B427" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>448</v>
+      </c>
+      <c r="B428" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>449</v>
+      </c>
+      <c r="B429" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>450</v>
+      </c>
+      <c r="B430" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>451</v>
+      </c>
+      <c r="B431" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>452</v>
+      </c>
+      <c r="B432" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>453</v>
+      </c>
+      <c r="B433" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>454</v>
+      </c>
+      <c r="B434" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>455</v>
+      </c>
+      <c r="B435" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>456</v>
+      </c>
+      <c r="B436" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B314" xr:uid="{42C3FECB-4F86-4C70-ACEE-A6019369A1F8}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>